--- a/data/trans_camb/P1404-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1404-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>8,23</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,97</t>
+          <t>7,8</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,59</t>
+          <t>3,44; 9,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,81</t>
+          <t>2,63; 8,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 11,48</t>
+          <t>5,03; 11,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,78</t>
+          <t>1,59; 8,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,61</t>
+          <t>1,51; 8,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 10,6</t>
+          <t>4,54; 10,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 8,15</t>
+          <t>3,37; 8,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,92</t>
+          <t>3,11; 7,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,1</t>
+          <t>5,77; 9,84</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122,94%</t>
+          <t>123,08%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,33; 178,43</t>
+          <t>42,39; 179,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,51; 165,18</t>
+          <t>32,69; 156,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,75; 216,42</t>
+          <t>64,28; 212,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 105,4</t>
+          <t>13,4; 107,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 99,64</t>
+          <t>12,16; 107,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,52; 132,37</t>
+          <t>38,91; 123,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,3; 113,39</t>
+          <t>34,42; 108,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,05; 110,54</t>
+          <t>32,58; 106,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,32; 138,82</t>
+          <t>58,75; 133,62</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>4,95</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>4,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 5,09</t>
+          <t>-0,3; 5,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 5,79</t>
+          <t>0,45; 5,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 6,11</t>
+          <t>2,13; 7,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 5,71</t>
+          <t>-0,28; 6,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,65</t>
+          <t>-0,04; 6,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,26</t>
+          <t>1,51; 6,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,42</t>
+          <t>0,58; 4,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,38</t>
+          <t>1,23; 5,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 5,4</t>
+          <t>2,67; 6,41</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 66,32</t>
+          <t>-4,18; 65,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 76,6</t>
+          <t>2,55; 73,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 74,33</t>
+          <t>20,61; 97,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 56,33</t>
+          <t>-2,06; 61,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 66,72</t>
+          <t>-0,1; 65,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 75,68</t>
+          <t>11,01; 67,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 48,49</t>
+          <t>4,76; 50,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,55; 56,5</t>
+          <t>9,84; 58,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 57,72</t>
+          <t>23,45; 70,48</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,34</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,86</t>
+          <t>5,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,86</t>
+          <t>-0,56; 6,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,08</t>
+          <t>2,04; 8,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,22</t>
+          <t>4,94; 11,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,16</t>
+          <t>-1,39; 5,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,53</t>
+          <t>-2,74; 3,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 55,96</t>
+          <t>-0,41; 5,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,87</t>
+          <t>-0,13; 4,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,11</t>
+          <t>0,43; 4,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 43,89</t>
+          <t>3,24; 7,57</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108,56%</t>
+          <t>108,3%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>196,77%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>173,93%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 97,32</t>
+          <t>-7,86; 102,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,7; 136,11</t>
+          <t>21,87; 137,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,71; 180,86</t>
+          <t>52,22; 190,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 54,39</t>
+          <t>-11,73; 58,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 38,42</t>
+          <t>-22,83; 42,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 590,63</t>
+          <t>-3,89; 60,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 60,72</t>
+          <t>-1,6; 56,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,96; 63,36</t>
+          <t>4,6; 62,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47,7; 482,4</t>
+          <t>30,84; 95,58</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,02</t>
+          <t>8,61</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>7,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,71</t>
+          <t>0,23; 5,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,7</t>
+          <t>-1,14; 3,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 8,49</t>
+          <t>2,88; 8,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,25</t>
+          <t>1,24; 6,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,89</t>
+          <t>0,3; 5,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,95</t>
+          <t>5,92; 10,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,51</t>
+          <t>1,68; 5,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,03</t>
+          <t>0,28; 4,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,14</t>
+          <t>5,47; 9,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,23; 82,55</t>
+          <t>2,67; 80,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 53,32</t>
+          <t>-13,62; 50,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,02; 122,58</t>
+          <t>30,79; 114,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,87; 91,93</t>
+          <t>10,36; 87,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 72,57</t>
+          <t>3,08; 72,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,74; 139,73</t>
+          <t>54,6; 139,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,5; 70,8</t>
+          <t>16,81; 73,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 51,48</t>
+          <t>2,99; 52,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49,13; 119,78</t>
+          <t>57,05; 119,44</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,4</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>6,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,85</t>
+          <t>2,04; 5,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,04</t>
+          <t>2,19; 4,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,13</t>
+          <t>5,05; 7,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,15</t>
+          <t>1,79; 5,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,49</t>
+          <t>1,24; 4,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 25,02</t>
+          <t>4,35; 7,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,56</t>
+          <t>2,4; 4,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,31</t>
+          <t>2,17; 4,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,09; 17,18</t>
+          <t>5,15; 7,19</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>100,95%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>21,72; 66,84</t>
+          <t>23,92; 68,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25,63; 68,73</t>
+          <t>25,25; 67,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33,69; 97,01</t>
+          <t>58,08; 108,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,7; 54,43</t>
+          <t>16,46; 52,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,85; 46,84</t>
+          <t>11,17; 47,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,02; 252,33</t>
+          <t>39,41; 79,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,36; 52,46</t>
+          <t>24,84; 50,87</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>22,61; 50,27</t>
+          <t>22,37; 49,36</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>54,87; 186,31</t>
+          <t>53,01; 83,48</t>
         </is>
       </c>
     </row>
